--- a/expired_domains_TLD_net_final.xlsx
+++ b/expired_domains_TLD_net_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\DNS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD834ED4-B271-4199-96D7-811CFA215EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0F909B4-D59A-4CC9-8DBB-B825BECE1819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="224">
   <si>
     <t>City</t>
   </si>
@@ -583,9 +583,6 @@
     <t>199.34.228.74</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>Fargo</t>
   </si>
   <si>
@@ -604,9 +601,6 @@
     <t>64.29.17.65</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>Independence</t>
   </si>
   <si>
@@ -652,9 +646,6 @@
     <t>AntiochSelfStorage.net</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Allen</t>
   </si>
   <si>
@@ -701,12 +692,6 @@
   </si>
   <si>
     <t>172.67.189.230</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
 </sst>
 </file>
@@ -1048,6 +1033,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="69.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -2194,8 +2191,8 @@
       <c r="H36" t="s">
         <v>17</v>
       </c>
-      <c r="I36" t="s">
-        <v>194</v>
+      <c r="I36">
+        <v>9</v>
       </c>
       <c r="J36" t="s">
         <v>28</v>
@@ -2226,8 +2223,8 @@
       <c r="H37" t="s">
         <v>17</v>
       </c>
-      <c r="I37" t="s">
-        <v>227</v>
+      <c r="I37">
+        <v>10</v>
       </c>
       <c r="J37" t="s">
         <v>28</v>
@@ -2258,8 +2255,8 @@
       <c r="H38" t="s">
         <v>17</v>
       </c>
-      <c r="I38" t="s">
-        <v>187</v>
+      <c r="I38">
+        <v>8</v>
       </c>
       <c r="J38" t="s">
         <v>28</v>
@@ -2290,8 +2287,8 @@
       <c r="H39" t="s">
         <v>17</v>
       </c>
-      <c r="I39" t="s">
-        <v>227</v>
+      <c r="I39">
+        <v>10</v>
       </c>
       <c r="J39" t="s">
         <v>28</v>
@@ -2322,8 +2319,8 @@
       <c r="H40" t="s">
         <v>17</v>
       </c>
-      <c r="I40" t="s">
-        <v>228</v>
+      <c r="I40">
+        <v>7</v>
       </c>
       <c r="J40" t="s">
         <v>28</v>
@@ -2395,25 +2392,25 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>187</v>
+      </c>
+      <c r="B43" t="s">
         <v>188</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>189</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>190</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" t="s">
         <v>191</v>
       </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>192</v>
-      </c>
-      <c r="G43" t="s">
-        <v>193</v>
       </c>
       <c r="H43" t="s">
         <v>23</v>
@@ -2427,16 +2424,16 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>193</v>
+      </c>
+      <c r="B44" t="s">
+        <v>194</v>
+      </c>
+      <c r="C44" t="s">
         <v>195</v>
       </c>
-      <c r="B44" t="s">
+      <c r="D44" t="s">
         <v>196</v>
-      </c>
-      <c r="C44" t="s">
-        <v>197</v>
-      </c>
-      <c r="D44" t="s">
-        <v>198</v>
       </c>
       <c r="E44" t="s">
         <v>14</v>
@@ -2445,7 +2442,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2459,25 +2456,25 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" t="s">
         <v>200</v>
       </c>
-      <c r="B45" t="s">
+      <c r="D45" t="s">
         <v>201</v>
       </c>
-      <c r="C45" t="s">
+      <c r="E45" t="s">
+        <v>14</v>
+      </c>
+      <c r="F45" t="s">
         <v>202</v>
       </c>
-      <c r="D45" t="s">
+      <c r="G45" t="s">
         <v>203</v>
-      </c>
-      <c r="E45" t="s">
-        <v>14</v>
-      </c>
-      <c r="F45" t="s">
-        <v>204</v>
-      </c>
-      <c r="G45" t="s">
-        <v>205</v>
       </c>
       <c r="H45" t="s">
         <v>23</v>
@@ -2491,16 +2488,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
+      </c>
+      <c r="C46" t="s">
         <v>206</v>
       </c>
-      <c r="B46" t="s">
+      <c r="D46" t="s">
         <v>207</v>
-      </c>
-      <c r="C46" t="s">
-        <v>208</v>
-      </c>
-      <c r="D46" t="s">
-        <v>209</v>
       </c>
       <c r="E46" t="s">
         <v>14</v>
@@ -2514,8 +2511,8 @@
       <c r="H46" t="s">
         <v>23</v>
       </c>
-      <c r="I46" t="s">
-        <v>210</v>
+      <c r="I46">
+        <v>1</v>
       </c>
       <c r="J46" t="s">
         <v>28</v>
@@ -2523,31 +2520,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>208</v>
+      </c>
+      <c r="B47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C47" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" t="s">
         <v>211</v>
       </c>
-      <c r="B47" t="s">
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47" t="s">
+        <v>202</v>
+      </c>
+      <c r="G47" t="s">
         <v>212</v>
       </c>
-      <c r="C47" t="s">
-        <v>213</v>
-      </c>
-      <c r="D47" t="s">
-        <v>214</v>
-      </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
-      <c r="F47" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" t="s">
-        <v>215</v>
-      </c>
       <c r="H47" t="s">
         <v>23</v>
       </c>
-      <c r="I47" t="s">
-        <v>210</v>
+      <c r="I47">
+        <v>1</v>
       </c>
       <c r="J47" t="s">
         <v>28</v>
@@ -2555,16 +2552,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" t="s">
+        <v>215</v>
+      </c>
+      <c r="D48" t="s">
         <v>216</v>
-      </c>
-      <c r="B48" t="s">
-        <v>217</v>
-      </c>
-      <c r="C48" t="s">
-        <v>218</v>
-      </c>
-      <c r="D48" t="s">
-        <v>219</v>
       </c>
       <c r="E48" t="s">
         <v>14</v>
@@ -2573,7 +2570,7 @@
         <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H48" t="s">
         <v>23</v>
@@ -2587,25 +2584,25 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>218</v>
+      </c>
+      <c r="B49" t="s">
+        <v>219</v>
+      </c>
+      <c r="C49" t="s">
+        <v>220</v>
+      </c>
+      <c r="D49" t="s">
         <v>221</v>
       </c>
-      <c r="B49" t="s">
+      <c r="E49" t="s">
+        <v>14</v>
+      </c>
+      <c r="F49" t="s">
         <v>222</v>
       </c>
-      <c r="C49" t="s">
+      <c r="G49" t="s">
         <v>223</v>
-      </c>
-      <c r="D49" t="s">
-        <v>224</v>
-      </c>
-      <c r="E49" t="s">
-        <v>14</v>
-      </c>
-      <c r="F49" t="s">
-        <v>225</v>
-      </c>
-      <c r="G49" t="s">
-        <v>226</v>
       </c>
       <c r="H49" t="s">
         <v>23</v>
